--- a/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/ConsolidatedTrialBalanceExcel.xlsx
+++ b/Dynamics BC Excel Reports/ReportLayouts/Excel/GeneralLedger/ConsolidatedTrialBalanceExcel.xlsx
@@ -1,111 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr hidePivotFieldList="1"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <x:workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daniel.williams\Source\Gold\Yellowstone.Apps\Apps\W1\ExcelReports\app\ReportLayouts\Excel\GeneralLedger\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB10CD7E-34E5-43D8-B576-49F592A14DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="755" xr2:uid="{6D6330EC-2177-4A25-AEDD-C3F019032741}"/>
-  </bookViews>
-  <sheets>
-    <sheet name="$ConsolidatedTrialBalPrint$" sheetId="20" r:id="rId1"/>
-    <sheet name="$TrialBalanceLCY$" sheetId="6" r:id="rId2"/>
-    <sheet name="$TrialBalanceACY$" sheetId="18" r:id="rId3"/>
-    <sheet name="$ByBusinessUnitLCY$" sheetId="10" r:id="rId4"/>
-    <sheet name="$ByBusinessUnitACY$" sheetId="19" r:id="rId5"/>
-    <sheet name="$AboutTheReportLabel$" sheetId="21" r:id="rId6"/>
-    <sheet name="GLAccounts" sheetId="16" state="hidden" r:id="rId7"/>
-    <sheet name="Dimension1" sheetId="14" state="hidden" r:id="rId8"/>
-    <sheet name="Dimension2" sheetId="15" state="hidden" r:id="rId9"/>
-    <sheet name="BusinessUnits" sheetId="17" state="hidden" r:id="rId10"/>
-    <sheet name="TrialBalanceData" sheetId="4" state="hidden" r:id="rId11"/>
-    <sheet name="CaptionData" sheetId="5" state="hidden" r:id="rId12"/>
-    <sheet name="TranslationData" sheetId="12" state="hidden" r:id="rId13"/>
-    <sheet name="NamedMetadata" sheetId="13" state="hidden" r:id="rId14"/>
-    <sheet name="Aggregated Metadata" sheetId="3" state="hidden" r:id="rId15"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxBusinessUnits1" hidden="1">BusinessUnits[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxDimension11" hidden="1">Dimension1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxDimension21" hidden="1">Dimension2[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxGLAccounts1" hidden="1">GLAccounts[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxTrialBalanceData1" hidden="1">TrialBalanceData[]</definedName>
-    <definedName name="CompanyName">NamedMetadata!$A$1</definedName>
-    <definedName name="DataRetrieved">#REF!</definedName>
-    <definedName name="DataRetrievedCaption">NamedMetadata!$A$7</definedName>
-    <definedName name="EndingDate">NamedMetadata!$A$4</definedName>
-    <definedName name="PeriodCaption">NamedMetadata!$A$5</definedName>
-    <definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</definedName>
-    <definedName name="RetrievedAt">NamedMetadata!$A$2</definedName>
-    <definedName name="Slicer_AccountCategory1">#N/A</definedName>
-    <definedName name="Slicer_AccountCategory11">#N/A</definedName>
-    <definedName name="Slicer_AccountCategory2">#N/A</definedName>
-    <definedName name="Slicer_AccountCategory21">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory1">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory11">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory2">#N/A</definedName>
-    <definedName name="Slicer_AccountSubcategory21">#N/A</definedName>
-    <definedName name="Slicer_BusinessUnitCode1">#N/A</definedName>
-    <definedName name="Slicer_BusinessUnitCode11">#N/A</definedName>
-    <definedName name="Slicer_Code">#N/A</definedName>
-    <definedName name="Slicer_Code1">#N/A</definedName>
-    <definedName name="Slicer_Dim1Code">#N/A</definedName>
-    <definedName name="Slicer_Dim1Code1">#N/A</definedName>
-    <definedName name="Slicer_Dim2Code">#N/A</definedName>
-    <definedName name="Slicer_Dim2Code1">#N/A</definedName>
-    <definedName name="Slicer_Dimension1Code1">#N/A</definedName>
-    <definedName name="Slicer_Dimension1Code11">#N/A</definedName>
-    <definedName name="Slicer_Dimension2Code1">#N/A</definedName>
-    <definedName name="Slicer_Dimension2Code11">#N/A</definedName>
-    <definedName name="Slicer_IncomeBalance1">#N/A</definedName>
-    <definedName name="Slicer_IncomeBalance11">#N/A</definedName>
-    <definedName name="Slicer_IncomeBalance2">#N/A</definedName>
-    <definedName name="Slicer_IncomeBalance21">#N/A</definedName>
-    <definedName name="StartingDate">NamedMetadata!$A$3</definedName>
-    <definedName name="TEMP" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",#REF!,#REF!,"none")</definedName>
-    <definedName name="TEMP2" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",#REF!,#REF!,"none")</definedName>
-    <definedName name="UntilCaption">NamedMetadata!$A$6</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId16"/>
-    <pivotCache cacheId="16" r:id="rId17"/>
-    <pivotCache cacheId="20" r:id="rId18"/>
-    <pivotCache cacheId="24" r:id="rId19"/>
-    <pivotCache cacheId="27" r:id="rId20"/>
-  </pivotCaches>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
+  <x:bookViews>
+    <x:workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="755" xr2:uid="{6D6330EC-2177-4A25-AEDD-C3F019032741}"/>
+  </x:bookViews>
+  <x:sheets>
+    <x:sheet name="$ConsolidatedTrialBalPrint$" sheetId="20" r:id="rId1"/>
+    <x:sheet name="$TrialBalanceLCY$" sheetId="6" r:id="rId2"/>
+    <x:sheet name="$TrialBalanceACY$" sheetId="18" r:id="rId3"/>
+    <x:sheet name="$ByBusinessUnitLCY$" sheetId="10" r:id="rId4"/>
+    <x:sheet name="$ByBusinessUnitACY$" sheetId="19" r:id="rId5"/>
+    <x:sheet name="$AboutTheReportLabel$" sheetId="21" r:id="rId6"/>
+    <x:sheet name="GLAccounts" sheetId="16" state="hidden" r:id="rId7"/>
+    <x:sheet name="Dimension1" sheetId="14" state="hidden" r:id="rId8"/>
+    <x:sheet name="Dimension2" sheetId="15" state="hidden" r:id="rId9"/>
+    <x:sheet name="BusinessUnits" sheetId="17" state="hidden" r:id="rId10"/>
+    <x:sheet name="TrialBalanceData" sheetId="4" state="hidden" r:id="rId11"/>
+    <x:sheet name="CaptionData" sheetId="5" state="hidden" r:id="rId12"/>
+    <x:sheet name="TranslationData" sheetId="12" state="hidden" r:id="rId13"/>
+    <x:sheet name="NamedMetadata" sheetId="13" state="hidden" r:id="rId14"/>
+    <x:sheet name="Aggregated Metadata" sheetId="3" state="hidden" r:id="rId15"/>
+  </x:sheets>
+  <x:definedNames>
+    <x:definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxBusinessUnits1" hidden="1">BusinessUnits[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxDimension11" hidden="1">Dimension1[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxDimension21" hidden="1">Dimension2[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxGLAccounts1" hidden="1">GLAccounts[]</x:definedName>
+    <x:definedName name="_xlcn.WorksheetConnection_modifiedlayout.xlsxTrialBalanceData1" hidden="1">TrialBalanceData[]</x:definedName>
+    <x:definedName name="CompanyName">NamedMetadata!$A$1</x:definedName>
+    <x:definedName name="DataRetrieved">#REF!</x:definedName>
+    <x:definedName name="DataRetrievedCaption">NamedMetadata!$A$7</x:definedName>
+    <x:definedName name="EndingDate">NamedMetadata!$A$4</x:definedName>
+    <x:definedName name="PeriodCaption">NamedMetadata!$A$5</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportText" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.AboutThisReportTitle" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionName" comment="Use this function to get the Extension Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionPublisher" comment="Use this function to get the Extension Publisher from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Publisher",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ExtensionVersion" comment="Use this function to get the Extension Version from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Extension Version",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectID" comment="Use this function to get the Object ID from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object ID",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ObjectName" comment="Use this function to get the Object Name from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Object Name",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportMetadata.ReportHelpLink" comment="Use this function to get the Report help link from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Report help link",ReportMetadataValues[[#All],[Report Property]],ReportMetadataValues[[#All],[Report Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyId" comment="Use this function to get the Company Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.CompanyName" comment="Use this function to get the Company name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Company name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Date" comment="Use this function to get the Date from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Date",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentName" comment="Use this function to get the Environment name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.EnvironmentType" comment="Use this function to get the Environment type from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Environment type",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.FormatRegion" comment="Use this function to get the Format Region from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Format Region",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.Language" comment="Use this function to get the Language from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Language",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantEntraId" comment="Use this function to get the Tenant Entra Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Entra Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.TenantId" comment="Use this function to get the Tenant Id from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("Tenant Id",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="ReportRequest.UserName" comment="Use this function to get the User name from the ReportRequestValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("User name",ReportRequestValues[[#All],[Request Property]],ReportRequestValues[[#All],[Request Property Value]],"none")</x:definedName>
+    <x:definedName name="RetrievedAt">NamedMetadata!$A$2</x:definedName>
+    <x:definedName name="Slicer_AccountCategory1">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountCategory11">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountCategory2">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountCategory21">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory1">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory11">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory2">#N/A</x:definedName>
+    <x:definedName name="Slicer_AccountSubcategory21">#N/A</x:definedName>
+    <x:definedName name="Slicer_BusinessUnitCode1">#N/A</x:definedName>
+    <x:definedName name="Slicer_BusinessUnitCode11">#N/A</x:definedName>
+    <x:definedName name="Slicer_Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dim1Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dim1Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dim2Code">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dim2Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension1Code11">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2Code1">#N/A</x:definedName>
+    <x:definedName name="Slicer_Dimension2Code11">#N/A</x:definedName>
+    <x:definedName name="Slicer_IncomeBalance1">#N/A</x:definedName>
+    <x:definedName name="Slicer_IncomeBalance11">#N/A</x:definedName>
+    <x:definedName name="Slicer_IncomeBalance2">#N/A</x:definedName>
+    <x:definedName name="Slicer_IncomeBalance21">#N/A</x:definedName>
+    <x:definedName name="StartingDate">NamedMetadata!$A$3</x:definedName>
+    <x:definedName name="TEMP" comment="Use this function to get the About This Report Text from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Text",#REF!,#REF!,"none")</x:definedName>
+    <x:definedName name="TEMP2" comment="Use this function to get the About This Report Title from the ReportMetadataValues table in the Aggregated Metadata worksheet">_xlfn.XLOOKUP("About This Report Title",#REF!,#REF!,"none")</x:definedName>
+    <x:definedName name="UntilCaption">NamedMetadata!$A$6</x:definedName>
+  </x:definedNames>
+  <x:calcPr calcId="191029"/>
+  <x:pivotCaches>
+    <x:pivotCache cacheId="12" r:id="rId16"/>
+    <x:pivotCache cacheId="16" r:id="rId17"/>
+    <x:pivotCache cacheId="20" r:id="rId18"/>
+    <x:pivotCache cacheId="24" r:id="rId19"/>
+    <x:pivotCache cacheId="27" r:id="rId20"/>
+  </x:pivotCaches>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="11" r:id="rId21"/>
-        <pivotCache cacheId="15" r:id="rId22"/>
-        <pivotCache cacheId="19" r:id="rId23"/>
-        <pivotCache cacheId="23" r:id="rId24"/>
+        <x:pivotCache cacheId="11" r:id="rId21"/>
+        <x:pivotCache cacheId="15" r:id="rId22"/>
+        <x:pivotCache cacheId="19" r:id="rId23"/>
+        <x:pivotCache cacheId="23" r:id="rId24"/>
       </x14:pivotCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
         <x14:slicerCache r:id="rId25"/>
         <x14:slicerCache r:id="rId26"/>
@@ -132,14 +132,14 @@
         <x14:slicerCache r:id="rId47"/>
         <x14:slicerCache r:id="rId48"/>
       </x14:slicerCaches>
-    </ext>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+    </x:ext>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
+    </x:ext>
+    <x:ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
       <x15:dataModel>
         <x15:modelTables>
           <x15:modelTable id="TrialBalanceData  3_8fc52510-8dbf-4d6b-968e-eafd3813e21c" name="TrialBalanceData  3" connection="Query - TrialBalanceDataPrint"/>
@@ -156,8 +156,8 @@
           <x15:modelRelationship fromTable="TrialBalanceData" fromColumn="BusinessUnitCode" toTable="BusinessUnits" toColumn="Code"/>
         </x15:modelRelationships>
       </x15:dataModel>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+    </x:ext>
+    <x:ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
@@ -167,9 +167,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+    </x:ext>
+  </x:extLst>
+</x:workbook>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8377,20 +8377,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{5E0ADD72-BF24-4C74-896B-F0B33D417A20}" name="GLAccounts" displayName="GLAccounts" ref="A1:H2" totalsRowShown="0" headerRowDxfId="179">
-  <autoFilter ref="A1:H2" xr:uid="{5E0ADD72-BF24-4C74-896B-F0B33D417A20}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{ACE19F5D-A569-4D61-B3AA-F949BB6F1089}" name="AccountNumber"/>
-    <tableColumn id="2" xr3:uid="{16E17622-30AC-490B-A02D-D8DC531D73F2}" name="AccountName"/>
-    <tableColumn id="3" xr3:uid="{1DC1A141-9F4B-463B-A02F-DAC3AE94BD40}" name="IncomeBalance"/>
-    <tableColumn id="4" xr3:uid="{1E66CEC2-FA5F-4A66-B7EF-3B216321CFEE}" name="AccountCategory"/>
-    <tableColumn id="5" xr3:uid="{72F3DABF-01A1-495C-B2E9-45DE026B8B18}" name="AccountSubcategory"/>
-    <tableColumn id="6" xr3:uid="{8CA92E2F-F55C-4E93-B055-6385FE2AC79C}" name="AccountType"/>
-    <tableColumn id="7" xr3:uid="{1A3A02C9-6E8D-4257-BBC5-CA00B72FAFAB}" name="Indentation"/>
-    <tableColumn id="8" xr3:uid="{132D04BD-FBF9-4E2D-9872-E2B5418FDD1B}" name="IndentedAccountName"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="GLAccounts" displayName="GLAccounts" ref="A1:H2" totalsRowShown="0" headerRowDxfId="179" xr:uid="{5E0ADD72-BF24-4C74-896B-F0B33D417A20}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:H2" xr:uid="{5E0ADD72-BF24-4C74-896B-F0B33D417A20}"/>
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="AccountNumber" xr3:uid="{ACE19F5D-A569-4D61-B3AA-F949BB6F1089}"/>
+    <x:tableColumn id="2" name="AccountName" xr3:uid="{16E17622-30AC-490B-A02D-D8DC531D73F2}"/>
+    <x:tableColumn id="3" name="IncomeBalance" xr3:uid="{1DC1A141-9F4B-463B-A02F-DAC3AE94BD40}"/>
+    <x:tableColumn id="4" name="AccountCategory" xr3:uid="{1E66CEC2-FA5F-4A66-B7EF-3B216321CFEE}"/>
+    <x:tableColumn id="5" name="AccountSubcategory" xr3:uid="{72F3DABF-01A1-495C-B2E9-45DE026B8B18}"/>
+    <x:tableColumn id="6" name="AccountType" xr3:uid="{8CA92E2F-F55C-4E93-B055-6385FE2AC79C}"/>
+    <x:tableColumn id="7" name="Indentation" xr3:uid="{1A3A02C9-6E8D-4257-BBC5-CA00B72FAFAB}"/>
+    <x:tableColumn id="8" name="IndentedAccountName" xr3:uid="{132D04BD-FBF9-4E2D-9872-E2B5418FDD1B}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8416,53 +8416,53 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{C52F78E1-E1D4-4EFA-9992-7AF6CB9FD863}" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="178">
-  <autoFilter ref="A1:B2" xr:uid="{C52F78E1-E1D4-4EFA-9992-7AF6CB9FD863}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E16CC07B-57D0-4E34-B8FF-130823791971}" name="Dim1Code"/>
-    <tableColumn id="2" xr3:uid="{118534BA-C413-462D-92AD-6AE85A444712}" name="Dim1Name"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Dimension1" displayName="Dimension1" ref="A1:B2" totalsRowShown="0" headerRowDxfId="178" xr:uid="{C52F78E1-E1D4-4EFA-9992-7AF6CB9FD863}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{C52F78E1-E1D4-4EFA-9992-7AF6CB9FD863}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim1Code" xr3:uid="{E16CC07B-57D0-4E34-B8FF-130823791971}"/>
+    <x:tableColumn id="2" name="Dim1Name" xr3:uid="{118534BA-C413-462D-92AD-6AE85A444712}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{104414AE-5E17-4DC6-A61F-B47CFDC10258}" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="177">
-  <autoFilter ref="A1:B2" xr:uid="{104414AE-5E17-4DC6-A61F-B47CFDC10258}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3E4798FA-DF9F-4265-97F0-71A44E0CF882}" name="Dim2Code"/>
-    <tableColumn id="2" xr3:uid="{FF6F98D3-D145-43F8-8AFE-EA92B2588CEB}" name="Dim2Name"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Dimension2" displayName="Dimension2" ref="A1:B2" totalsRowShown="0" headerRowDxfId="177" xr:uid="{104414AE-5E17-4DC6-A61F-B47CFDC10258}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{104414AE-5E17-4DC6-A61F-B47CFDC10258}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Dim2Code" xr3:uid="{3E4798FA-DF9F-4265-97F0-71A44E0CF882}"/>
+    <x:tableColumn id="2" name="Dim2Name" xr3:uid="{FF6F98D3-D145-43F8-8AFE-EA92B2588CEB}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{373D78FE-93C6-4F1A-8593-8DF4DCB0B71E}" name="BusinessUnits" displayName="BusinessUnits" ref="A1:B2" totalsRowShown="0" headerRowDxfId="176">
-  <autoFilter ref="A1:B2" xr:uid="{373D78FE-93C6-4F1A-8593-8DF4DCB0B71E}"/>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5C3000E8-482D-4405-949E-FDECF4EADE3B}" name="Code"/>
-    <tableColumn id="2" xr3:uid="{C100E8B7-B185-4D18-A9E5-6CB6E5C44E81}" name="Name"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="BusinessUnits" displayName="BusinessUnits" ref="A1:B2" totalsRowShown="0" headerRowDxfId="176" xr:uid="{373D78FE-93C6-4F1A-8593-8DF4DCB0B71E}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:B2" xr:uid="{373D78FE-93C6-4F1A-8593-8DF4DCB0B71E}"/>
+  <x:tableColumns count="2">
+    <x:tableColumn id="1" name="Code" xr3:uid="{5C3000E8-482D-4405-949E-FDECF4EADE3B}"/>
+    <x:tableColumn id="2" name="Name" xr3:uid="{C100E8B7-B185-4D18-A9E5-6CB6E5C44E81}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0E3D0719-BDB0-45F8-AF22-7F9CB4F9795D}" name="TrialBalanceData" displayName="TrialBalanceData" ref="A1:H2" totalsRowShown="0" headerRowDxfId="175">
-  <autoFilter ref="A1:H2" xr:uid="{0E3D0719-BDB0-45F8-AF22-7F9CB4F9795D}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{5C5EC385-921B-4B37-89C0-7359D4AE1C53}" name="Account" dataDxfId="174"/>
-    <tableColumn id="2" xr3:uid="{DAFAF1DA-C7F6-4473-A8EE-B6D8E6777983}" name="Dimension1Code" dataDxfId="173"/>
-    <tableColumn id="3" xr3:uid="{8637D9C6-BA2D-40C3-84D4-26776F04D696}" name="Dimension2Code" dataDxfId="172"/>
-    <tableColumn id="4" xr3:uid="{84A7443B-E085-4802-AC9A-E3303EBE3777}" name="NetChange"/>
-    <tableColumn id="5" xr3:uid="{6B5E46EC-8728-4639-9644-D89E4E7346F4}" name="Balance"/>
-    <tableColumn id="6" xr3:uid="{0E550D4F-F274-4026-8DF8-8562DD4FF402}" name="NetChangeACY"/>
-    <tableColumn id="7" xr3:uid="{2015841F-D2FE-4A2F-9EF1-E0A2654C1763}" name="BalanceACY"/>
-    <tableColumn id="8" xr3:uid="{60DDE773-C84F-4A57-90B8-30DC844FA05E}" name="BusinessUnitCode"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
+<x:table xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="TrialBalanceData" displayName="TrialBalanceData" ref="A1:H2" totalsRowShown="0" headerRowDxfId="175" xr:uid="{0E3D0719-BDB0-45F8-AF22-7F9CB4F9795D}" mc:Ignorable="xr xr3">
+  <x:autoFilter ref="A1:H2" xr:uid="{0E3D0719-BDB0-45F8-AF22-7F9CB4F9795D}"/>
+  <x:tableColumns count="8">
+    <x:tableColumn id="1" name="Account" dataDxfId="174" xr3:uid="{5C5EC385-921B-4B37-89C0-7359D4AE1C53}"/>
+    <x:tableColumn id="2" name="Dimension1Code" dataDxfId="173" xr3:uid="{DAFAF1DA-C7F6-4473-A8EE-B6D8E6777983}"/>
+    <x:tableColumn id="3" name="Dimension2Code" dataDxfId="172" xr3:uid="{8637D9C6-BA2D-40C3-84D4-26776F04D696}"/>
+    <x:tableColumn id="4" name="NetChange" xr3:uid="{84A7443B-E085-4802-AC9A-E3303EBE3777}"/>
+    <x:tableColumn id="5" name="Balance" xr3:uid="{6B5E46EC-8728-4639-9644-D89E4E7346F4}"/>
+    <x:tableColumn id="6" name="NetChangeACY" xr3:uid="{0E550D4F-F274-4026-8DF8-8562DD4FF402}"/>
+    <x:tableColumn id="7" name="BalanceACY" xr3:uid="{2015841F-D2FE-4A2F-9EF1-E0A2654C1763}"/>
+    <x:tableColumn id="8" name="BusinessUnitCode" xr3:uid="{60DDE773-C84F-4A57-90B8-30DC844FA05E}"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
